--- a/data/Microsoft_10k_Source_Data.xlsx
+++ b/data/Microsoft_10k_Source_Data.xlsx
@@ -19,7 +19,7 @@
     <t xml:space="preserve">Year </t>
   </si>
   <si>
-    <t>Source Filling</t>
+    <t>Source Filing</t>
   </si>
   <si>
     <r>
